--- a/E/BRE03D.xlsx
+++ b/E/BRE03D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="301">
   <si>
     <t/>
   </si>
@@ -94,9 +94,6 @@
     <t>7</t>
   </si>
   <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
     <t>20021935</t>
   </si>
   <si>
@@ -604,6 +601,12 @@
     <t>CHOCODRINK BLG 6'S</t>
   </si>
   <si>
+    <t>20143503</t>
+  </si>
+  <si>
+    <t>CHOCLTOS MTCHA 5'S</t>
+  </si>
+  <si>
     <t>20131214</t>
   </si>
   <si>
@@ -724,6 +727,12 @@
     <t>K/API KOPI SUSU10X31</t>
   </si>
   <si>
+    <t>20127276</t>
+  </si>
+  <si>
+    <t>LWK KOPI MURNI 9'S</t>
+  </si>
+  <si>
     <t>20046081</t>
   </si>
   <si>
@@ -850,15 +859,21 @@
     <t>K/API KOPI SPCL 150G</t>
   </si>
   <si>
+    <t>20143384</t>
+  </si>
+  <si>
+    <t>K/A BLCK COFE SPR10S</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>20136451</t>
   </si>
   <si>
     <t>NSCAFE AMERICANO 10S</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>20142007</t>
   </si>
   <si>
@@ -899,12 +914,6 @@
   </si>
   <si>
     <t>KAPAL API SPECIAL 90</t>
-  </si>
-  <si>
-    <t>20127276</t>
-  </si>
-  <si>
-    <t>LWK KOPI MURNI 9'S</t>
   </si>
 </sst>
 </file>
@@ -1297,14 +1306,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F137"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1464,15 +1473,15 @@
         <v>26</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -1481,7 +1490,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>19</v>
@@ -1489,10 +1498,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -1509,10 +1518,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1529,10 +1538,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1549,10 +1558,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1569,10 +1578,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1589,10 +1598,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1609,10 +1618,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1629,10 +1638,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1641,7 +1650,7 @@
         <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>19</v>
@@ -1649,10 +1658,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1661,7 +1670,7 @@
         <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>15</v>
@@ -1669,10 +1678,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1681,7 +1690,7 @@
         <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>19</v>
@@ -1689,10 +1698,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1701,7 +1710,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -1709,10 +1718,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1721,7 +1730,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>23</v>
@@ -1729,10 +1738,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1741,7 +1750,7 @@
         <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>19</v>
@@ -1749,10 +1758,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1769,10 +1778,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1789,10 +1798,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1809,10 +1818,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1829,10 +1838,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1849,10 +1858,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1869,10 +1878,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1889,10 +1898,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1901,7 +1910,7 @@
         <v>11</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>15</v>
@@ -1909,10 +1918,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1921,7 +1930,7 @@
         <v>11</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>15</v>
@@ -1929,10 +1938,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -1941,7 +1950,7 @@
         <v>11</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>15</v>
@@ -1949,10 +1958,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1961,7 +1970,7 @@
         <v>11</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -1969,10 +1978,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1981,7 +1990,7 @@
         <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>15</v>
@@ -1989,10 +1998,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -2001,7 +2010,7 @@
         <v>11</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>23</v>
@@ -2009,10 +2018,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -2021,7 +2030,7 @@
         <v>11</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>19</v>
@@ -2029,10 +2038,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -2041,7 +2050,7 @@
         <v>11</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>19</v>
@@ -2049,10 +2058,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2061,7 +2070,7 @@
         <v>11</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>23</v>
@@ -2069,10 +2078,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2089,10 +2098,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2109,10 +2118,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2129,10 +2138,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2149,10 +2158,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2169,10 +2178,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2189,10 +2198,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2209,10 +2218,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2221,7 +2230,7 @@
         <v>14</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>23</v>
@@ -2229,10 +2238,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2244,15 +2253,15 @@
         <v>4</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2264,15 +2273,15 @@
         <v>8</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2289,10 +2298,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2309,10 +2318,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2329,10 +2338,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2349,10 +2358,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>127</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2369,10 +2378,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2389,10 +2398,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2409,10 +2418,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2429,10 +2438,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2449,10 +2458,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -2469,10 +2478,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2489,10 +2498,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2509,10 +2518,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2529,10 +2538,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>145</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2549,10 +2558,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>147</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2569,10 +2578,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>149</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2589,10 +2598,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2601,7 +2610,7 @@
         <v>26</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -2609,10 +2618,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -2621,7 +2630,7 @@
         <v>26</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>19</v>
@@ -2629,10 +2638,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2641,18 +2650,18 @@
         <v>26</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2661,7 +2670,7 @@
         <v>26</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>19</v>
@@ -2669,16 +2678,16 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>4</v>
@@ -2689,16 +2698,16 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>8</v>
@@ -2709,16 +2718,16 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>11</v>
@@ -2729,16 +2738,16 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>4</v>
@@ -2749,16 +2758,16 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>8</v>
@@ -2769,16 +2778,16 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>11</v>
@@ -2789,16 +2798,16 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>14</v>
@@ -2809,36 +2818,36 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>22</v>
@@ -2849,96 +2858,96 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>11</v>
@@ -2949,56 +2958,56 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>22</v>
@@ -3009,16 +3018,16 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>4</v>
@@ -3029,16 +3038,16 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>8</v>
@@ -3049,16 +3058,16 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>11</v>
@@ -3069,16 +3078,16 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>14</v>
@@ -3089,16 +3098,16 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>18</v>
@@ -3109,59 +3118,59 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>23</v>
@@ -3169,19 +3178,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>23</v>
@@ -3189,19 +3198,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>23</v>
@@ -3209,19 +3218,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>23</v>
@@ -3229,19 +3238,19 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>23</v>
@@ -3249,19 +3258,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>23</v>
@@ -3269,19 +3278,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>23</v>
@@ -3289,19 +3298,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>23</v>
@@ -3309,179 +3318,179 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>182</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>23</v>
+        <v>181</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3489,39 +3498,39 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>23</v>
@@ -3529,19 +3538,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>23</v>
@@ -3549,19 +3558,19 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>23</v>
@@ -3569,39 +3578,39 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>23</v>
@@ -3609,19 +3618,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>23</v>
@@ -3629,19 +3638,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>23</v>
@@ -3649,59 +3658,59 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3709,99 +3718,99 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>23</v>
@@ -3809,79 +3818,79 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>281</v>
+        <v>95</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>23</v>
@@ -3889,19 +3898,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>281</v>
+        <v>95</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>23</v>
@@ -3909,39 +3918,39 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="E131" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>23</v>
@@ -3949,19 +3958,19 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>23</v>
@@ -3969,82 +3978,122 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>291</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>5</v>
+      <c r="B138" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/E/BRE03D.xlsx
+++ b/E/BRE03D.xlsx
@@ -868,6 +868,12 @@
     <t>17</t>
   </si>
   <si>
+    <t>20017575</t>
+  </si>
+  <si>
+    <t>NESCAFE CLSC 10X2G</t>
+  </si>
+  <si>
     <t>20136451</t>
   </si>
   <si>
@@ -884,12 +890,6 @@
   </si>
   <si>
     <t>NESCAFE CLASSIC 100G</t>
-  </si>
-  <si>
-    <t>20017575</t>
-  </si>
-  <si>
-    <t>NESCAFE CLSC 10X2G</t>
   </si>
   <si>
     <t>10005302</t>
@@ -3993,7 +3993,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4013,7 +4013,7 @@
         <v>18</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
